--- a/simple_game_test/final_test_summary_with_rounds.xlsx
+++ b/simple_game_test/final_test_summary_with_rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,6 +4024,636 @@
         <v>8</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>6</v>
+      </c>
+      <c r="E87" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>6</v>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>6</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
